--- a/test_doc/new_org/students_roster.xlsx
+++ b/test_doc/new_org/students_roster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -538,12 +533,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -590,12 +580,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -642,12 +627,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -694,12 +674,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,12 +721,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -798,12 +768,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -850,12 +815,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -902,12 +862,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -954,12 +909,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1009,11 +959,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1061,11 +1006,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1113,11 +1053,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1165,11 +1100,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1217,11 +1147,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1269,11 +1194,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1321,11 +1241,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1373,11 +1288,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1425,11 +1335,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1477,11 +1382,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1529,11 +1429,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1581,11 +1476,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1633,11 +1523,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1685,11 +1570,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1737,11 +1617,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1789,11 +1664,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1841,11 +1711,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -1893,11 +1758,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1945,11 +1805,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1997,11 +1852,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Hosteller</t>
@@ -2025,132 +1875,6 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>9833010030</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Zoya Ansari</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NG1901</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Day Scholar</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Mr Ansari</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>9822099001</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Mrs Ansari</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>9833099001</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NG1902</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Day Scholar</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Mr X</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>9822099002</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Rohan Kulkarni</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Day Scholar</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Mr Kulkarni</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>9822099003</t>
         </is>
       </c>
     </row>

--- a/test_doc/new_org/students_roster.xlsx
+++ b/test_doc/new_org/students_roster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aarav Patel</t>
+          <t>Yuvan Naidu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NG1001</t>
+          <t>NG4711</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,39 +491,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mr Patel</t>
+          <t>Mr Naidu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9822010001</t>
+          <t>9634124985</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Mrs Patel</t>
+          <t>Mrs Naidu</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9833010001</t>
+          <t>9473595608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Diya Iyer</t>
+          <t>Kabir Nair</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NG1002</t>
+          <t>NG4712</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -543,34 +543,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mr Iyer</t>
+          <t>Mr Nair</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9822010002</t>
+          <t>9273203567</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mrs Iyer</t>
+          <t>Mrs Nair</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9833010002</t>
+          <t>9354535131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vihaan Das</t>
+          <t>Ananya Verma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NG1003</t>
+          <t>NG4713</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,34 +590,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mr Das</t>
+          <t>Mr Verma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9822010003</t>
+          <t>9532618347</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mrs Das</t>
+          <t>Mrs Verma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9833010003</t>
+          <t>9699379140</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ananya Nair</t>
+          <t>Kavya Iyer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NG1004</t>
+          <t>NG4714</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -632,39 +632,39 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Iyer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9822010004</t>
+          <t>9845364212</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Iyer</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9833010004</t>
+          <t>9725119021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kabir Roy</t>
+          <t>Kavya Joshi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NG1005</t>
+          <t>NG4715</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -679,39 +679,39 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Day Scholar</t>
+          <t>Hosteller</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mr Roy</t>
+          <t>Mr Joshi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9822010005</t>
+          <t>9559020722</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mrs Roy</t>
+          <t>Mrs Joshi</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9833010005</t>
+          <t>9722084184</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ishita Patel</t>
+          <t>Navya Das</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NG1006</t>
+          <t>NG4716</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -731,34 +731,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mr Patel</t>
+          <t>Mr Das</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9822010006</t>
+          <t>9793355171</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Mrs Patel</t>
+          <t>Mrs Das</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9833010006</t>
+          <t>9391767216</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reyansh Iyer</t>
+          <t>Arjun Gupta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NG1007</t>
+          <t>NG4717</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -773,39 +773,39 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mr Iyer</t>
+          <t>Mr Gupta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9822010007</t>
+          <t>9454817341</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mrs Iyer</t>
+          <t>Mrs Gupta</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9833010007</t>
+          <t>9697854438</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sara Das</t>
+          <t>Nitara Naidu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NG1008</t>
+          <t>NG4718</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -825,34 +825,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mr Das</t>
+          <t>Mr Naidu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9822010008</t>
+          <t>9718012407</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mrs Das</t>
+          <t>Mrs Naidu</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9833010008</t>
+          <t>9876641316</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Advait Nair</t>
+          <t>Saanvi Verma</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NG1009</t>
+          <t>NG4719</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Verma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9822010009</t>
+          <t>9878966998</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Verma</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9833010009</t>
+          <t>9652395612</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Myra Roy</t>
+          <t>Ishita Iyer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NG1010</t>
+          <t>NG4720</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -914,143 +914,143 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mr Roy</t>
+          <t>Mr Iyer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9822010010</t>
+          <t>9981826494</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mrs Roy</t>
+          <t>Mrs Iyer</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9833010010</t>
+          <t>9179839633</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aarav Patel</t>
+          <t>Aditya Kumar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NG1011</t>
+          <t>NG4721</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mr Patel</t>
+          <t>Mr Kumar</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9822010011</t>
+          <t>9825950082</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mrs Patel</t>
+          <t>Mrs Kumar</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9833010011</t>
+          <t>9209196559</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Diya Iyer</t>
+          <t>Ishaan Pillai</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NG1012</t>
+          <t>NG4722</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Day Scholar</t>
+          <t>Hosteller</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mr Iyer</t>
+          <t>Mr Pillai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9822010012</t>
+          <t>9100611119</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mrs Iyer</t>
+          <t>Mrs Pillai</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9833010012</t>
+          <t>9528246452</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vihaan Das</t>
+          <t>Ishita Shetty</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NG1013</t>
+          <t>NG4723</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1060,86 +1060,86 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mr Das</t>
+          <t>Mr Shetty</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9822010013</t>
+          <t>9602726644</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mrs Das</t>
+          <t>Mrs Shetty</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9833010013</t>
+          <t>9498314504</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ananya Nair</t>
+          <t>Aisha Mehta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NG1014</t>
+          <t>NG4724</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Mehta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9822010014</t>
+          <t>9394032284</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Mehta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9833010014</t>
+          <t>9227365068</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kabir Roy</t>
+          <t>Diya Kumar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NG1015</t>
+          <t>NG4725</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1154,86 +1154,86 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mr Roy</t>
+          <t>Mr Kumar</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9822010015</t>
+          <t>9333737146</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mrs Roy</t>
+          <t>Mrs Kumar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9833010015</t>
+          <t>9691055474</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ishita Patel</t>
+          <t>Navya Reddy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NG1016</t>
+          <t>NG4726</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Day Scholar</t>
+          <t>Hosteller</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mr Patel</t>
+          <t>Mr Reddy</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9822010016</t>
+          <t>9131459270</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mrs Patel</t>
+          <t>Mrs Reddy</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9833010016</t>
+          <t>9510700660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reyansh Iyer</t>
+          <t>Avni Das</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NG1017</t>
+          <t>NG4727</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,44 +1243,44 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mr Iyer</t>
+          <t>Mr Das</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9822010017</t>
+          <t>9791831750</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mrs Iyer</t>
+          <t>Mrs Das</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9833010017</t>
+          <t>9674480458</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sara Das</t>
+          <t>Dhruv Gupta</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NG1018</t>
+          <t>NG4728</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1295,39 +1295,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mr Das</t>
+          <t>Mr Gupta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9822010018</t>
+          <t>9778078015</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mrs Das</t>
+          <t>Mrs Gupta</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9833010018</t>
+          <t>9511459001</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Advait Nair</t>
+          <t>Kavya Patel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NG1019</t>
+          <t>NG4729</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1342,39 +1342,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Patel</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9822010019</t>
+          <t>9448921628</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Patel</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9833010019</t>
+          <t>9908934862</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Myra Roy</t>
+          <t>Tara Gupta</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NG1020</t>
+          <t>NG4730</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1384,54 +1384,54 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mr Roy</t>
+          <t>Mr Gupta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9822010020</t>
+          <t>9134958429</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mrs Roy</t>
+          <t>Mrs Gupta</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9833010020</t>
+          <t>9796424242</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aarav Patel</t>
+          <t>Pari Patel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NG1021</t>
+          <t>NG4731</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9822010021</t>
+          <t>9756157403</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1451,29 +1451,29 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9833010021</t>
+          <t>9446370504</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Diya Iyer</t>
+          <t>Aisha Iyer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NG1022</t>
+          <t>NG4732</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9822010022</t>
+          <t>9647060559</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1498,29 +1498,29 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9833010022</t>
+          <t>9145499425</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vihaan Das</t>
+          <t>Rohan Das</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NG1023</t>
+          <t>NG4733</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9822010023</t>
+          <t>9909252040</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1545,76 +1545,76 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9833010023</t>
+          <t>9779300894</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ananya Nair</t>
+          <t>Pari Kulkarni</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NG1024</t>
+          <t>NG4734</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Kulkarni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9822010024</t>
+          <t>9124964670</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Kulkarni</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9833010024</t>
+          <t>9179038780</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kabir Roy</t>
+          <t>Aisha Pillai</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NG1025</t>
+          <t>NG4735</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1624,46 +1624,46 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mr Roy</t>
+          <t>Mr Pillai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9822010025</t>
+          <t>9112678266</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mrs Roy</t>
+          <t>Mrs Pillai</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9833010025</t>
+          <t>9393170285</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ishita Patel</t>
+          <t>Anika Nair</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NG1026</t>
+          <t>NG4736</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Day Scholar</t>
@@ -1671,86 +1671,86 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mr Patel</t>
+          <t>Mr Nair</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9822010026</t>
+          <t>9774792214</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mrs Patel</t>
+          <t>Mrs Nair</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9833010026</t>
+          <t>9355422846</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reyansh Iyer</t>
+          <t>Rudra Verma</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NG1027</t>
+          <t>NG4737</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hosteller</t>
+          <t>Day Scholar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mr Iyer</t>
+          <t>Mr Verma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9822010027</t>
+          <t>9784010307</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mrs Iyer</t>
+          <t>Mrs Verma</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9833010027</t>
+          <t>9383399320</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sara Das</t>
+          <t>Ayaan Patel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NG1028</t>
+          <t>NG4738</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1760,44 +1760,44 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Day Scholar</t>
+          <t>Hosteller</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mr Das</t>
+          <t>Mr Patel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9822010028</t>
+          <t>9657433328</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mrs Das</t>
+          <t>Mrs Patel</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9833010028</t>
+          <t>9463081217</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advait Nair</t>
+          <t>Ishita Kulkarni</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NG1029</t>
+          <t>NG4739</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1812,69 +1812,1197 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mr Nair</t>
+          <t>Mr Kulkarni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9822010029</t>
+          <t>9497649407</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mrs Nair</t>
+          <t>Mrs Kulkarni</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9833010029</t>
+          <t>9253182018</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Myra Roy</t>
+          <t>Kiara Shetty</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NG1030</t>
+          <t>NG4740</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Mr Shetty</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>9471689122</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mrs Shetty</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>9934244067</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Reyansh Sharma</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NG4741</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Mr Sharma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>9564709539</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mrs Sharma</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>9609161722</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Krishna Kumar</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NG4742</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Mr Kumar</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>9304721193</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Mrs Kumar</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>9389956474</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Aisha Das</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NG4743</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Mr Das</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>9828268437</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mrs Das</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9941742313</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tara Gupta</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NG4744</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Mr Gupta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>9203137634</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Mrs Gupta</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>9216943929</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kavya Mehta</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NG4745</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Mr Mehta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>9385413548</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Mrs Mehta</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>9606206970</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Aisha Joshi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NG4746</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Mr Joshi</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>9101776667</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Mrs Joshi</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>9246120734</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Saanvi Malhotra</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NG4747</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Mr Malhotra</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>9296646191</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Mrs Malhotra</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>9670847338</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rudra Rao</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NG4748</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Hosteller</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Mr Rao</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9556558616</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Mrs Rao</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>9217346083</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nitara Kulkarni</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NG4749</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Hosteller</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mr Kulkarni</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9776471702</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Mrs Kulkarni</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9887554484</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Advait Khan</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NG4750</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Mr Khan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9875966716</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Mrs Khan</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9716433310</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aarav Das</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NG4751</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Mr Das</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>9415685698</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mrs Das</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>9154257332</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Neel Sharma</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NG4752</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mr Sharma</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9311101978</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Mrs Sharma</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9940640688</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Saanvi Roy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NG4753</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Mr Roy</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>9822010030</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9655242655</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Mrs Roy</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>9833010030</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9652871713</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Anika Gupta</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NG4754</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mr Gupta</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9413930405</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mrs Gupta</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>9582186207</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Anika Gupta</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NG4755</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Mr Gupta</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9213829599</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mrs Gupta</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9278754034</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Anaya Sinha</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NG4756</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hosteller</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mr Sinha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>9316284984</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Mrs Sinha</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>9388355676</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dhruv Mehta</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NG4757</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Mr Mehta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>9510429680</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Mrs Mehta</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>9521447813</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Neel Mehta</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NG4758</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Mr Mehta</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>9469426923</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Mrs Mehta</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>9388081218</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Veer Gupta</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NG4759</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hosteller</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Mr Gupta</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>9297938792</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mrs Gupta</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>9799818182</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Atharv Kulkarni</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NG4760</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Hosteller</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Mr Kulkarni</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>9525203098</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mrs Kulkarni</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>9856072412</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Avni Banerjee</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NG4761</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Hosteller</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Mr Banerjee</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>9141104235</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Mrs Banerjee</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>9180894612</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Arjun Shetty</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NG4762</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Mr Shetty</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>9636875434</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mrs Shetty</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>9226849513</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tara Sinha</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NG4763</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Mr Sinha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9930072674</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mrs Sinha</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9483045714</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vivaan Joshi</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NG4764</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Day Scholar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Mr Joshi</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9759586373</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mrs Joshi</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>9888571857</t>
         </is>
       </c>
     </row>
